--- a/data/nest_issues_commented/FP_nest_data_issues_220825.xlsx
+++ b/data/nest_issues_commented/FP_nest_data_issues_220825.xlsx
@@ -534,7 +534,7 @@
     <t xml:space="preserve">138.32261600000001</t>
   </si>
   <si>
-    <t xml:space="preserve">Nest habitat is not beach, dune, foredune/face, estuary/spit, or rocks; </t>
+    <t xml:space="preserve">Nest habitat is not beach, dune, foredune/face, or estuary/spit; </t>
   </si>
   <si>
     <t xml:space="preserve">201819</t>

--- a/data/nest_issues_commented/FP_nest_data_issues_220825.xlsx
+++ b/data/nest_issues_commented/FP_nest_data_issues_220825.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
   <si>
     <t xml:space="preserve">season</t>
   </si>
@@ -372,46 +372,49 @@
     <t xml:space="preserve">27112011</t>
   </si>
   <si>
+    <t xml:space="preserve">24112011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Shelley Beach (lady bay)_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01012012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02012012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watsons Gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Watsons Gap_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27092011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30092011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01102011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signnest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Watsons Gap_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08112011</t>
+  </si>
+  <si>
     <t xml:space="preserve">01122011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201112_Shelley Beach (lady bay)_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01012012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02012012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Watsons Gap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201112_Watsons Gap_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27092011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30092011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01102011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">signnest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201112_Watsons Gap_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08112011</t>
   </si>
   <si>
     <t xml:space="preserve">-35.535842</t>
@@ -2037,22 +2040,22 @@
         <v>102</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>40878</v>
+        <v>40871</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>40874</v>
+        <v>40843</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>40878</v>
+        <v>40871</v>
       </c>
       <c r="S14" t="n">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="T14" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="U14" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2278,10 +2281,10 @@
         <v>132</v>
       </c>
       <c r="E17" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="F17" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="G17" t="s">
         <v>78</v>
@@ -2296,10 +2299,10 @@
         <v>68</v>
       </c>
       <c r="K17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>40887</v>
@@ -2356,7 +2359,7 @@
         <v>44</v>
       </c>
       <c r="AE17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF17" t="s">
         <v>87</v>
@@ -2364,22 +2367,22 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G18" t="s">
         <v>38</v>
@@ -2394,10 +2397,10 @@
         <v>26</v>
       </c>
       <c r="K18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -2456,22 +2459,22 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G19" t="s">
         <v>38</v>
@@ -2486,10 +2489,10 @@
         <v>68</v>
       </c>
       <c r="K19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -2540,7 +2543,7 @@
         <v>44</v>
       </c>
       <c r="AE19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AF19" t="s">
         <v>87</v>
